--- a/OMOP Analysis/Results/Yearly/yearly_combined_summary_costs_OMOP.xlsx
+++ b/OMOP Analysis/Results/Yearly/yearly_combined_summary_costs_OMOP.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O9"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -441,43 +441,43 @@
         <v>1</v>
       </c>
       <c r="C2">
-        <v>521.33</v>
+        <v>710.01</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>8348.219999999999</v>
+        <v>15909.51</v>
       </c>
       <c r="F2">
-        <v>478.85</v>
+        <v>676.04</v>
       </c>
       <c r="G2">
-        <v>196.59</v>
+        <v>254.94</v>
       </c>
       <c r="H2">
-        <v>392.86</v>
+        <v>529.0599999999999</v>
       </c>
       <c r="I2">
-        <v>697.03</v>
+        <v>951.77</v>
       </c>
       <c r="J2">
         <v>22900</v>
       </c>
       <c r="K2">
-        <v>11938415.66</v>
+        <v>16259129.83</v>
       </c>
       <c r="L2">
-        <v>521.33</v>
+        <v>710.01</v>
       </c>
       <c r="M2">
-        <v>3.16</v>
+        <v>4.47</v>
       </c>
       <c r="N2">
-        <v>515.13</v>
+        <v>701.25</v>
       </c>
       <c r="O2">
-        <v>527.53</v>
+        <v>718.76</v>
       </c>
     </row>
     <row r="3">
@@ -490,337 +490,141 @@
         <v>2</v>
       </c>
       <c r="C3">
-        <v>439</v>
+        <v>609.38</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
       <c r="E3">
-        <v>5911.47</v>
+        <v>9341.540000000001</v>
       </c>
       <c r="F3">
-        <v>452.76</v>
+        <v>639.0700000000001</v>
       </c>
       <c r="G3">
-        <v>124.1</v>
+        <v>171.91</v>
       </c>
       <c r="H3">
-        <v>315.43</v>
+        <v>435.31</v>
       </c>
       <c r="I3">
-        <v>603.5599999999999</v>
+        <v>836.13</v>
       </c>
       <c r="J3">
         <v>14172</v>
       </c>
       <c r="K3">
-        <v>6221502.85</v>
+        <v>8636096.98</v>
       </c>
       <c r="L3">
-        <v>271.68</v>
+        <v>377.12</v>
       </c>
       <c r="M3">
-        <v>3.8</v>
+        <v>5.37</v>
       </c>
       <c r="N3">
-        <v>431.54</v>
+        <v>598.85</v>
       </c>
       <c r="O3">
-        <v>446.45</v>
+        <v>619.9</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>All Patients &amp; relevant encounters</t>
+          <t>Users &amp; all encounters</t>
         </is>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4">
-        <v>450.65</v>
+        <v>728.72</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
       <c r="E4">
-        <v>8322.77</v>
+        <v>15909.51</v>
       </c>
       <c r="F4">
-        <v>437.66</v>
+        <v>675.17</v>
       </c>
       <c r="G4">
-        <v>151.3</v>
+        <v>277.01</v>
       </c>
       <c r="H4">
-        <v>333</v>
+        <v>545.7</v>
       </c>
       <c r="I4">
-        <v>606.5700000000001</v>
+        <v>967.73</v>
       </c>
       <c r="J4">
-        <v>22900</v>
+        <v>22302</v>
       </c>
       <c r="K4">
-        <v>10319856.46</v>
+        <v>16251961.38</v>
       </c>
       <c r="L4">
-        <v>450.65</v>
+        <v>728.72</v>
       </c>
       <c r="M4">
-        <v>2.89</v>
+        <v>4.52</v>
       </c>
       <c r="N4">
-        <v>444.98</v>
+        <v>719.86</v>
       </c>
       <c r="O4">
-        <v>456.32</v>
+        <v>737.58</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>All Patients &amp; relevant encounters</t>
+          <t>Users &amp; all encounters</t>
         </is>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5">
-        <v>385.9</v>
+        <v>614.13</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
       <c r="E5">
-        <v>5465.25</v>
+        <v>9341.540000000001</v>
       </c>
       <c r="F5">
-        <v>410.09</v>
+        <v>639.29</v>
       </c>
       <c r="G5">
-        <v>111</v>
+        <v>176.95</v>
       </c>
       <c r="H5">
-        <v>269</v>
+        <v>441.46</v>
       </c>
       <c r="I5">
-        <v>531.37</v>
+        <v>840.64</v>
       </c>
       <c r="J5">
-        <v>14172</v>
+        <v>14062</v>
       </c>
       <c r="K5">
-        <v>5468987.9</v>
+        <v>8635953.529999999</v>
       </c>
       <c r="L5">
-        <v>238.82</v>
+        <v>387.23</v>
       </c>
       <c r="M5">
-        <v>3.44</v>
+        <v>5.39</v>
       </c>
       <c r="N5">
-        <v>379.15</v>
+        <v>603.5700000000001</v>
       </c>
       <c r="O5">
-        <v>392.65</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Users &amp; all encounters</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-      <c r="C6">
-        <v>536.5599999999999</v>
-      </c>
-      <c r="D6">
-        <v>0</v>
-      </c>
-      <c r="E6">
-        <v>8348.219999999999</v>
-      </c>
-      <c r="F6">
-        <v>477.98</v>
-      </c>
-      <c r="G6">
-        <v>210.83</v>
-      </c>
-      <c r="H6">
-        <v>407</v>
-      </c>
-      <c r="I6">
-        <v>710.75</v>
-      </c>
-      <c r="J6">
-        <v>22218</v>
-      </c>
-      <c r="K6">
-        <v>11921330.54</v>
-      </c>
-      <c r="L6">
-        <v>536.5599999999999</v>
-      </c>
-      <c r="M6">
-        <v>3.21</v>
-      </c>
-      <c r="N6">
-        <v>530.28</v>
-      </c>
-      <c r="O6">
-        <v>542.85</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Users &amp; all encounters</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>2</v>
-      </c>
-      <c r="C7">
-        <v>442.94</v>
-      </c>
-      <c r="D7">
-        <v>0</v>
-      </c>
-      <c r="E7">
-        <v>5911.47</v>
-      </c>
-      <c r="F7">
-        <v>452.89</v>
-      </c>
-      <c r="G7">
-        <v>127.73</v>
-      </c>
-      <c r="H7">
-        <v>318.88</v>
-      </c>
-      <c r="I7">
-        <v>606.52</v>
-      </c>
-      <c r="J7">
-        <v>14045</v>
-      </c>
-      <c r="K7">
-        <v>6221101.53</v>
-      </c>
-      <c r="L7">
-        <v>280</v>
-      </c>
-      <c r="M7">
-        <v>3.82</v>
-      </c>
-      <c r="N7">
-        <v>435.45</v>
-      </c>
-      <c r="O7">
-        <v>450.43</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Users &amp; relevant encounters</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-      <c r="C8">
-        <v>464.48</v>
-      </c>
-      <c r="D8">
-        <v>0</v>
-      </c>
-      <c r="E8">
-        <v>8322.77</v>
-      </c>
-      <c r="F8">
-        <v>437.03</v>
-      </c>
-      <c r="G8">
-        <v>172.55</v>
-      </c>
-      <c r="H8">
-        <v>343</v>
-      </c>
-      <c r="I8">
-        <v>619.45</v>
-      </c>
-      <c r="J8">
-        <v>22218</v>
-      </c>
-      <c r="K8">
-        <v>10319856.46</v>
-      </c>
-      <c r="L8">
-        <v>464.48</v>
-      </c>
-      <c r="M8">
-        <v>2.93</v>
-      </c>
-      <c r="N8">
-        <v>458.73</v>
-      </c>
-      <c r="O8">
-        <v>470.23</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Users &amp; relevant encounters</t>
-        </is>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-      <c r="C9">
-        <v>389.39</v>
-      </c>
-      <c r="D9">
-        <v>0</v>
-      </c>
-      <c r="E9">
-        <v>5465.25</v>
-      </c>
-      <c r="F9">
-        <v>410.28</v>
-      </c>
-      <c r="G9">
-        <v>111</v>
-      </c>
-      <c r="H9">
-        <v>273.98</v>
-      </c>
-      <c r="I9">
-        <v>537.37</v>
-      </c>
-      <c r="J9">
-        <v>14045</v>
-      </c>
-      <c r="K9">
-        <v>5468987.9</v>
-      </c>
-      <c r="L9">
-        <v>246.15</v>
-      </c>
-      <c r="M9">
-        <v>3.46</v>
-      </c>
-      <c r="N9">
-        <v>382.6</v>
-      </c>
-      <c r="O9">
-        <v>396.18</v>
+        <v>624.7</v>
       </c>
     </row>
   </sheetData>
